--- a/config/demo/forms/app/breast_cancer_followup_actions.xlsx
+++ b/config/demo/forms/app/breast_cancer_followup_actions.xlsx
@@ -345,7 +345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="3" min="1" max="1"/>
@@ -491,29 +491,29 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="4">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>form_start_timestamp</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>once(if(${_id} != '', now(), ''))</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="4">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>form_sync_timestamp</t>
         </is>
@@ -1280,19 +1280,36 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>form_submit_timestamp</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>now()</t>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>form_submit_timestamp_iso</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>form_submit_timestamp_display</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%e-%b-%Y %H:%M:%S')</t>
         </is>
       </c>
     </row>
